--- a/artfynd/A 39080-2020 artfynd.xlsx
+++ b/artfynd/A 39080-2020 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 39080-2020 artfynd.xlsx
+++ b/artfynd/A 39080-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1011,6 +1011,239 @@
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>124934578</v>
+      </c>
+      <c r="B5" t="n">
+        <v>105117</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Tjärnberget, Mpd</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>594470</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6921126</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>15:47</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>15:47</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Maja Lundahl</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Maja Lundahl</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>124934740</v>
+      </c>
+      <c r="B6" t="n">
+        <v>79891</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Tjärnberget, Mpd</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>594470</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6921126</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>15:47</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>15:47</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>På stor sälg.</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Maja Lundahl</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Maja Lundahl</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 39080-2020 artfynd.xlsx
+++ b/artfynd/A 39080-2020 artfynd.xlsx
@@ -1013,10 +1013,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124934578</v>
+        <v>124934740</v>
       </c>
       <c r="B5" t="n">
-        <v>105117</v>
+        <v>79891</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1025,28 +1025,31 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221144</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Tjärnberget, Mpd</t>
@@ -1101,12 +1104,18 @@
           <t>15:47</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>På stor sälg.</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1125,10 +1134,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124934740</v>
+        <v>124934578</v>
       </c>
       <c r="B6" t="n">
-        <v>79891</v>
+        <v>105117</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1137,31 +1146,28 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>221144</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Tjärnberget, Mpd</t>
@@ -1216,18 +1222,12 @@
           <t>15:47</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>På stor sälg.</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 39080-2020 artfynd.xlsx
+++ b/artfynd/A 39080-2020 artfynd.xlsx
@@ -1013,10 +1013,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124934740</v>
+        <v>124934578</v>
       </c>
       <c r="B5" t="n">
-        <v>79891</v>
+        <v>105117</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1025,31 +1025,28 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>221144</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Tjärnberget, Mpd</t>
@@ -1104,18 +1101,12 @@
           <t>15:47</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>På stor sälg.</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1134,10 +1125,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124934578</v>
+        <v>124934740</v>
       </c>
       <c r="B6" t="n">
-        <v>105117</v>
+        <v>79891</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1146,28 +1137,31 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221144</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Tjärnberget, Mpd</t>
@@ -1222,12 +1216,18 @@
           <t>15:47</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>På stor sälg.</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 39080-2020 artfynd.xlsx
+++ b/artfynd/A 39080-2020 artfynd.xlsx
@@ -1013,10 +1013,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124934740</v>
+        <v>124934578</v>
       </c>
       <c r="B5" t="n">
-        <v>79891</v>
+        <v>105293</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1025,31 +1025,28 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>221144</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Tjärnberget, Mpd</t>
@@ -1104,18 +1101,12 @@
           <t>15:47</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>På stor sälg.</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1134,10 +1125,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124934578</v>
+        <v>124934740</v>
       </c>
       <c r="B6" t="n">
-        <v>105117</v>
+        <v>80028</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1146,28 +1137,31 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221144</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Tjärnberget, Mpd</t>
@@ -1222,12 +1216,18 @@
           <t>15:47</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>På stor sälg.</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 39080-2020 artfynd.xlsx
+++ b/artfynd/A 39080-2020 artfynd.xlsx
@@ -1013,10 +1013,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124934578</v>
+        <v>124934740</v>
       </c>
       <c r="B5" t="n">
-        <v>105293</v>
+        <v>80028</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1025,28 +1025,31 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221144</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Tjärnberget, Mpd</t>
@@ -1101,12 +1104,18 @@
           <t>15:47</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>På stor sälg.</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1125,10 +1134,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124934740</v>
+        <v>124934578</v>
       </c>
       <c r="B6" t="n">
-        <v>80028</v>
+        <v>105293</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1137,31 +1146,28 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>221144</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Tjärnberget, Mpd</t>
@@ -1216,18 +1222,12 @@
           <t>15:47</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>På stor sälg.</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 39080-2020 artfynd.xlsx
+++ b/artfynd/A 39080-2020 artfynd.xlsx
@@ -1013,43 +1013,35 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124934740</v>
+        <v>124934578</v>
       </c>
       <c r="B5" t="n">
-        <v>80028</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>105293</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>221144</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Tjärnberget, Mpd</t>
@@ -1104,18 +1096,12 @@
           <t>15:47</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>På stor sälg.</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1134,40 +1120,38 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124934578</v>
+        <v>124934740</v>
       </c>
       <c r="B6" t="n">
-        <v>105293</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80028</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221144</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Tjärnberget, Mpd</t>
@@ -1222,12 +1206,18 @@
           <t>15:47</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>På stor sälg.</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
